--- a/test_excels/2_datos_correctos_para_duplicar.xlsx
+++ b/test_excels/2_datos_correctos_para_duplicar.xlsx
@@ -1,10 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7F2404-B088-47F1-8F54-73821B9EB5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Usuarios" state="visible" r:id="rId4"/>
+    <sheet name="Usuarios" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -46,21 +50,9 @@
     <t>Titulo_Proyecto (Opcional)</t>
   </si>
   <si>
-    <t>Ana</t>
-  </si>
-  <si>
     <t>García</t>
   </si>
   <si>
-    <t>88888881</t>
-  </si>
-  <si>
-    <t>ana@ej.com</t>
-  </si>
-  <si>
-    <t>04141112233</t>
-  </si>
-  <si>
     <t>Clave1</t>
   </si>
   <si>
@@ -70,35 +62,63 @@
     <t/>
   </si>
   <si>
-    <t>Pedro</t>
-  </si>
-  <si>
     <t>Páez</t>
   </si>
   <si>
-    <t>88888882</t>
-  </si>
-  <si>
-    <t>pedro@ej.com</t>
-  </si>
-  <si>
-    <t>04241112233</t>
-  </si>
-  <si>
     <t>PROFESOR</t>
+  </si>
+  <si>
+    <t>santiago</t>
+  </si>
+  <si>
+    <t>victor</t>
+  </si>
+  <si>
+    <t>V-30407730</t>
+  </si>
+  <si>
+    <t>V-30520132</t>
+  </si>
+  <si>
+    <t>santiagomaldonado15@gmail.com</t>
+  </si>
+  <si>
+    <t>contrerasv174@gmail.com</t>
+  </si>
+  <si>
+    <t>+584141234567</t>
+  </si>
+  <si>
+    <t>+584241234567</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -118,13 +138,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -461,11 +486,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="21.453125" customWidth="1"/>
+    <col min="4" max="4" width="34.6328125" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -500,78 +530,82 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{C093FAC1-3CD8-492E-8B38-3FE697A43A4A}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{0A50545E-8F12-48C3-B6F8-FF9673E9D0B4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>